--- a/data/trans_camb/IQ2608_R3-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IQ2608_R3-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,12</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,32</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>15,16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,34</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16,58</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8,48</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,12</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,88</t>
+          <t>16,66</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12,41</t>
+          <t>12,19</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,42; 23,97</t>
+          <t>1,41; 15,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 12,04</t>
+          <t>-9,34; 7,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,05; 27,41</t>
+          <t>-11,79; 16,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,64; 16,23</t>
+          <t>7,65; 24,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 6,59</t>
+          <t>-5,6; 13,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 18,34</t>
+          <t>-6,05; 26,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 16,77</t>
+          <t>6,34; 16,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 7,64</t>
+          <t>-5,17; 6,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,81; 20,35</t>
+          <t>-1,68; 19,46</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,2%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-1,34%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,01%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>20,16%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>4,44%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>22,05%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,2%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-1,34%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9,16; 35,23</t>
+          <t>1,65; 20,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 17,14</t>
+          <t>-10,92; 9,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 39,23</t>
+          <t>-13,59; 21,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 21,02</t>
+          <t>9,44; 35,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 8,53</t>
+          <t>-6,96; 18,8</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 23,19</t>
+          <t>-5,7; 37,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,83; 22,28</t>
+          <t>7,61; 22,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 10,17</t>
+          <t>-6,3; 8,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 27,04</t>
+          <t>-1,86; 25,15</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18,71</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18,33</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4,08</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>20,9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>21,85</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>4,85</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18,71</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>18,33</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,48</t>
+          <t>2,98</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>4,74</t>
+          <t>3,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15,01; 27,17</t>
+          <t>12,81; 24,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,06; 28,3</t>
+          <t>12,4; 23,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,06; 16,46</t>
+          <t>-9,08; 16,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13,34; 24,59</t>
+          <t>14,94; 27,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>12,85; 23,94</t>
+          <t>16,1; 28,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 15,17</t>
+          <t>-11,21; 14,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,55; 24,32</t>
+          <t>15,63; 23,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,85; 24,06</t>
+          <t>15,62; 23,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 12,48</t>
+          <t>-5,79; 12,75</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27,46%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>26,91%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,99%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>31,37%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>32,8%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>27,46%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>26,91%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>21,37; 43,63</t>
+          <t>17,98; 38,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23,19; 45,23</t>
+          <t>17,6; 37,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 25,3</t>
+          <t>-12,4; 24,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18,47; 38,43</t>
+          <t>21,46; 43,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,44; 37,08</t>
+          <t>22,89; 45,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 23,28</t>
+          <t>-16,64; 22,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,3; 38,09</t>
+          <t>22,39; 36,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>22,72; 37,78</t>
+          <t>22,26; 36,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 18,78</t>
+          <t>-8,41; 19,23</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>11,76</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18,18</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6,86</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>29,47</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>31,39</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13,77</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11,76</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,18</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,76</t>
+          <t>11,83</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>10,5</t>
+          <t>9,72</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>20,74; 38,4</t>
+          <t>3,42; 21,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22,52; 39,7</t>
+          <t>9,28; 25,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 29,36</t>
+          <t>-7,96; 19,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,94; 20,82</t>
+          <t>20,52; 38,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,55; 26,29</t>
+          <t>22,98; 39,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 19,01</t>
+          <t>-2,28; 27,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,32; 26,72</t>
+          <t>14,36; 26,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,91; 30,03</t>
+          <t>18,6; 31,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 19,19</t>
+          <t>-0,59; 19,74</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>18,92%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>29,25%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11,03%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>61,56%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>65,57%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>28,78%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18,92%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>29,25%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>17,56%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,11; 92,76</t>
+          <t>5,06; 38,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42,42; 94,21</t>
+          <t>13,8; 46,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 66,78</t>
+          <t>-10,59; 33,67</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,2; 36,37</t>
+          <t>38,05; 92,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15,92; 47,11</t>
+          <t>42,24; 94,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 32,96</t>
+          <t>-4,24; 62,96</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,81; 51,82</t>
+          <t>24,36; 51,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>30,12; 58,52</t>
+          <t>31,83; 61,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 35,73</t>
+          <t>-0,9; 36,68</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>26,09</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33,64</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>13,6</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>13,66</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>19,29</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,81</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>26,09</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33,64</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,09</t>
+          <t>3,15</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9,01</t>
+          <t>8,77</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,66; 22,09</t>
+          <t>17,57; 33,76</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11,54; 27,35</t>
+          <t>25,95; 40,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-10,47; 15,84</t>
+          <t>2,28; 27,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18,87; 33,29</t>
+          <t>5,09; 21,16</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,82; 40,38</t>
+          <t>11,77; 27,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 26,05</t>
+          <t>-10,25; 16,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,51; 25,39</t>
+          <t>14,17; 25,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,36; 31,82</t>
+          <t>21,04; 32,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 17,17</t>
+          <t>-0,03; 17,67</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>53,43%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>68,89%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>27,85%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>25,17%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>35,56%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>53,43%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>68,89%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>9,99; 44,06</t>
+          <t>32,8; 76,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>19,72; 55,1</t>
+          <t>49,08; 91,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 31,14</t>
+          <t>4,56; 59,6</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>34,93; 75,01</t>
+          <t>9,11; 42,74</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>48,24; 91,66</t>
+          <t>20,13; 55,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,26; 56,01</t>
+          <t>-17,94; 30,58</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,77; 52,15</t>
+          <t>25,56; 53,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>38,99; 65,81</t>
+          <t>38,21; 67,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 34,31</t>
+          <t>-0,18; 35,24</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>18,28</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>19,69</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4,82</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>20,28</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>19,93</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>4,56</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>18,28</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>19,69</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,29</t>
+          <t>4,28</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>15,85; 23,97</t>
+          <t>14,55; 22,39</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,31; 24,11</t>
+          <t>15,67; 23,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 11,7</t>
+          <t>-2,29; 11,85</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>14,6; 22,03</t>
+          <t>16,15; 23,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15,74; 23,27</t>
+          <t>15,95; 23,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 12,23</t>
+          <t>-3,81; 10,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,67; 22,41</t>
+          <t>16,68; 21,92</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>17,38; 22,72</t>
+          <t>17,17; 22,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,47; 10,35</t>
+          <t>-1,22; 9,35</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>28,76%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>30,98%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7,58%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>33,48%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>32,89%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>7,53%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>28,76%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>30,98%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>25,38; 41,84</t>
+          <t>22,02; 36,57</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>25,82; 41,67</t>
+          <t>23,93; 38,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 19,49</t>
+          <t>-3,5; 18,89</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22,16; 36,21</t>
+          <t>25,8; 40,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>23,99; 37,97</t>
+          <t>25,25; 40,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 19,44</t>
+          <t>-6,19; 17,34</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,15; 37,19</t>
+          <t>26,2; 36,13</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>27,21; 37,53</t>
+          <t>26,9; 37,06</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>0,72; 16,86</t>
+          <t>-1,93; 15,51</t>
         </is>
       </c>
     </row>
